--- a/results/tables/excel/table_9_rule_comparison_random_summary.xlsx
+++ b/results/tables/excel/table_9_rule_comparison_random_summary.xlsx
@@ -425,311 +425,455 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rule_label</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>instances</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>guarantee_kept</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>worst_minimum_ratio_over_lambda_star</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median_minimum_ratio_over_lambda_star</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>median_total_delivery_relative_to_three_stage</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>median_temporal_variation_minus_three_stage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>share_users_better</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>share_users_worse</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>delivery_relative_p05</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>delivery_relative_p95</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>temporal_variation_difference_p05</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>temporal_variation_difference_p95</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>three_stage</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Three-stage lexicographic (proposed)</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>200</v>
-      </c>
       <c r="D2" t="n">
         <v>200</v>
       </c>
       <c r="E2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2" t="n">
         <v>0.9999999996004516</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>total_delivery_max</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Total-delivery maximization</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>200</v>
-      </c>
       <c r="D3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" t="n">
         <v>11</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.020735532458341</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1.480284376183015</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.480528511821975</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.4812239221140473</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.064768609066976</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.3548964830255498</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.744667411099431</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>equal_proportional</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Equal proportional allocation</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>200</v>
-      </c>
       <c r="D4" t="n">
         <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.4604843226465383</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-3.254999702742769</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.7809457579972183</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1828753509605924</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8849503983879327</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-10.02507812342839</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.7269713071436905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>weighted_sum_balanced</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Weighted single objective (35), (a,b,c) = (1,1,1)</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>200</v>
-      </c>
       <c r="D5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" t="n">
         <v>147</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.9999999999999999</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.8614521593602389</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-2.601353341896093</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.2260083449235049</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.6286509040333796</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5954406001681338</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9908632798654869</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-8.543682158677392</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.4958417783324123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>weighted_sum_efficiency</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Weighted single objective (35), (a,b,c) = (1,5,1)</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>200</v>
-      </c>
       <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="n">
         <v>107</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.9999999999999998</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.9837870998445756</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-1.656544764245015</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.325452016689847</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.5340751043115438</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7939454163893359</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-6.684111454618155</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.532107773982724e-15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>weighted_sum_guarantee</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Weighted single objective (35), (a,b,c) = (5,1,1)</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
       <c r="D7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" t="n">
         <v>191</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.9333116492510453</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.8562652539217737</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-2.594490205308214</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.2065368567454798</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.5695410292072323</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5899775254748647</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9892794394783816</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-8.622778008257553</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.4621539539684858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>leximin</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Full leximin (progressive filling)</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
       <c r="D8" t="n">
         <v>200</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.9907544381173621</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>-0.2389702169354209</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.5139082058414465</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.4527121001390821</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9505964332585596</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.003100861209039</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-3.079370548622815</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6635368514673333</v>
       </c>
     </row>
   </sheetData>
